--- a/exports/bookings-2026.xlsx
+++ b/exports/bookings-2026.xlsx
@@ -9214,9 +9214,19 @@
         <f>K260</f>
         <v/>
       </c>
-      <c r="M260" s="35" t="n"/>
-      <c r="N260" s="20" t="n"/>
-      <c r="O260" s="21" t="n"/>
+      <c r="M260" s="35" t="inlineStr">
+        <is>
+          <t>٧ مساءً إلى ٥ صباح</t>
+        </is>
+      </c>
+      <c r="N260" s="20" t="inlineStr">
+        <is>
+          <t>0503666853</t>
+        </is>
+      </c>
+      <c r="O260" s="21" t="n">
+        <v>400</v>
+      </c>
       <c r="P260" s="35" t="n"/>
       <c r="Q260" s="21" t="n"/>
       <c r="R260" s="19" t="n"/>
@@ -9289,9 +9299,19 @@
       <c r="D263" s="13" t="n"/>
       <c r="E263" s="50" t="n"/>
       <c r="F263" s="51" t="n"/>
-      <c r="G263" s="13" t="n"/>
-      <c r="H263" s="51" t="n"/>
-      <c r="I263" s="51" t="n"/>
+      <c r="G263" s="13" t="inlineStr">
+        <is>
+          <t>فترة 4</t>
+        </is>
+      </c>
+      <c r="H263" s="51" t="inlineStr">
+        <is>
+          <t>‪+966549031970‬</t>
+        </is>
+      </c>
+      <c r="I263" s="51" t="n">
+        <v>300</v>
+      </c>
       <c r="J263" s="99" t="n"/>
       <c r="K263" s="98" t="n"/>
       <c r="L263" s="100" t="n"/>
@@ -9316,9 +9336,19 @@
         <f>B264</f>
         <v/>
       </c>
-      <c r="D264" s="12" t="n"/>
-      <c r="E264" s="52" t="n"/>
-      <c r="F264" s="53" t="n"/>
+      <c r="D264" s="12" t="inlineStr">
+        <is>
+          <t>فترة 1</t>
+        </is>
+      </c>
+      <c r="E264" s="52" t="inlineStr">
+        <is>
+          <t>‪+966 55 969 6330‬</t>
+        </is>
+      </c>
+      <c r="F264" s="53" t="n">
+        <v>450</v>
+      </c>
       <c r="G264" s="12" t="n"/>
       <c r="H264" s="57" t="n"/>
       <c r="I264" s="57" t="n"/>
@@ -10129,9 +10159,19 @@
       <c r="D291" s="13" t="n"/>
       <c r="E291" s="50" t="n"/>
       <c r="F291" s="51" t="n"/>
-      <c r="G291" s="13" t="n"/>
-      <c r="H291" s="51" t="n"/>
-      <c r="I291" s="51" t="n"/>
+      <c r="G291" s="13" t="inlineStr">
+        <is>
+          <t>فترة 4</t>
+        </is>
+      </c>
+      <c r="H291" s="51" t="inlineStr">
+        <is>
+          <t>+966 54 556 9050</t>
+        </is>
+      </c>
+      <c r="I291" s="51" t="n">
+        <v>550</v>
+      </c>
       <c r="J291" s="99" t="n"/>
       <c r="K291" s="98" t="n"/>
       <c r="L291" s="100" t="n"/>

--- a/exports/bookings-2026.xlsx
+++ b/exports/bookings-2026.xlsx
@@ -9221,7 +9221,7 @@
       </c>
       <c r="N260" s="20" t="inlineStr">
         <is>
-          <t>0503666853</t>
+          <t>محجوز</t>
         </is>
       </c>
       <c r="O260" s="21" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="H263" s="51" t="inlineStr">
         <is>
-          <t>‪+966549031970‬</t>
+          <t>محجوز</t>
         </is>
       </c>
       <c r="I263" s="51" t="n">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="E264" s="52" t="inlineStr">
         <is>
-          <t>‪+966 55 969 6330‬</t>
+          <t>محجوز</t>
         </is>
       </c>
       <c r="F264" s="53" t="n">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="H291" s="51" t="inlineStr">
         <is>
-          <t>+966 54 556 9050</t>
+          <t>محجوز</t>
         </is>
       </c>
       <c r="I291" s="51" t="n">
